--- a/output/pdf_financials_xlsx/GUD.xlsx
+++ b/output/pdf_financials_xlsx/GUD.xlsx
@@ -7018,7 +7018,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -13174,7 +13178,11 @@
           <t>Prepaids and deposits 1,704 2,165</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -13566,7 +13574,11 @@
           <t>Prepaids and deposits 4,355 3,046</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -16928,7 +16940,11 @@
           <t>Prepaids and deposits 1,704</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -17244,7 +17260,11 @@
           <t>Prepaids and deposits 4,355</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GUD.xlsx
+++ b/output/pdf_financials_xlsx/GUD.xlsx
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-3.9</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-18.632</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-24.414</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-26.3</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1673,16 +1673,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>131.054</v>
+        <v>134.954</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>37.016</v>
+        <v>55.648</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>23.473</v>
+        <v>47.887</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>21.199</v>
+        <v>47.499</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>29.464</v>
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>131.117</v>
+        <v>135.017</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>37.14</v>
+        <v>55.772</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>23.91</v>
+        <v>48.324</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>22.828</v>
+        <v>49.128</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>31.396</v>
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>35922.46575342466</v>
+        <v>36990.95890410959</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>3581.485053037608</v>
+        <v>5378.206364513018</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>402.5252525252525</v>
+        <v>813.5353535353536</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>264.3965716933055</v>
+        <v>569.006254343294</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>251.168</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>283.445451</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>237.481</v>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>133.412</v>
+        <v>416.857451</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>471.207</v>
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>295.161</v>
+        <v>11.715549</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>23.819</v>
@@ -29336,7 +29336,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E301" s="5" t="n">
@@ -49666,7 +49666,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -54164,7 +54164,7 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
@@ -55232,7 +55232,7 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">

--- a/output/pdf_financials_xlsx/GUD.xlsx
+++ b/output/pdf_financials_xlsx/GUD.xlsx
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.063</v>
+        <v>0.022</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.124</v>
@@ -1739,13 +1739,13 @@
         <v>47.915</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>62.621</v>
+        <v>51.742</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>50.397</v>
+        <v>45.04</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>53.109</v>
+        <v>44.355</v>
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>135.017</v>
+        <v>134.976</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>55.772</v>
@@ -1786,13 +1786,13 @@
         <v>63.59</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>18.661</v>
+        <v>7.782</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>28.409</v>
+        <v>23.052</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>55.161</v>
+        <v>46.407</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>36990.95890410959</v>
+        <v>36979.72602739726</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>5378.206364513018</v>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>6.356727516751088</v>
+        <v>2.650879027670381</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>8.656028811787971</v>
+        <v>7.023787397280308</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>14.85602094240838</v>
+        <v>12.4983840734277</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0.124</v>
@@ -5484,13 +5484,13 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.924</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="113">
@@ -31828,7 +31828,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -43510,7 +43514,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -43586,7 +43594,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -47684,7 +47692,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -49300,7 +49312,7 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -53182,7 +53194,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -53252,7 +53268,7 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -54086,7 +54102,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
@@ -55078,7 +55094,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr"/>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E648" t="inlineStr">
         <is>
           <t>-</t>
@@ -55154,7 +55174,7 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -57576,7 +57596,11 @@
           <t>Depreciation of property and equipment [note9]</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E681" t="inlineStr">
         <is>
           <t>-</t>
@@ -57652,7 +57676,11 @@
           <t>Amortization of intangible assets [note10]</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr"/>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E682" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GUD.xlsx
+++ b/output/pdf_financials_xlsx/GUD.xlsx
@@ -3334,39 +3334,37 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.748</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.752</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>72.831</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>44.468</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>81.88800000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>59.735</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>37.783</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>47.388</v>
       </c>
     </row>
     <row r="65">
@@ -3469,39 +3467,37 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.499</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>2.377</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>2.459</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>4.484</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>5.348</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.293</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>18.479</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>25.475</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>27.399</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>43.004</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>76.36499999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5251,31 +5247,31 @@
         <v>4.421</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>3.038</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>2.137</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>3.045</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>1.888</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>2.327</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>8.114000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -5546,37 +5542,37 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-133.411</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-583.225</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-535.6849999999999</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-314.358</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-531.401</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0</v>
+        <v>-223.507</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-47.892</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-181.642</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-331.909</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-149.329</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-69.42700000000001</v>
       </c>
     </row>
     <row r="115">
@@ -5592,13 +5588,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>503.935</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>544.812</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>259.067</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -5635,7 +5631,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.75</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -5650,19 +5646,19 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-220.351</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-22.931</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-9.007999999999999</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-29.003</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-31.786</v>
       </c>
     </row>
     <row r="117">
@@ -30408,7 +30404,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -30482,7 +30482,11 @@
           <t>Share-based compensation expense 21 [ii]</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -31426,7 +31430,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -31482,7 +31490,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -33450,7 +33462,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -33520,7 +33536,11 @@
           <t>Share-based compensation expense 21 [ii]</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -34866,7 +34886,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -34940,7 +34964,11 @@
           <t>Share-based compensation expense 22 [ii]</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -36336,7 +36364,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -39888,7 +39920,11 @@
           <t>Share-based compensation expense 16 [ii]</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -41060,7 +41096,11 @@
           <t>Share-based compensation expense 14 [ii]</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -41574,7 +41614,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -44352,7 +44396,11 @@
           <t>Investing Activities Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -44500,7 +44548,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E507" t="inlineStr">
         <is>
           <t>-</t>
@@ -45030,7 +45082,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>-</t>
@@ -48384,7 +48440,11 @@
           <t>Net proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E558" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -50266,7 +50326,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr"/>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E584" t="inlineStr">
         <is>
           <t>-</t>
